--- a/data/trans_orig/P1412-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2012</t>
+          <t>Población con diagnóstico de angina de pecho en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>951606</t>
+          <t>952214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>967250</t>
+          <t>967300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1303512</t>
+          <t>1303929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1322888</t>
+          <t>1322640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2263341</t>
+          <t>2263794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2287367</t>
+          <t>2287052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20308</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1943649</t>
+          <t>1945364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959824</t>
+          <t>1959838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1745995</t>
+          <t>1746145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3694730</t>
+          <t>3695521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3711608</t>
+          <t>3712351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1418,97 +1418,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5933</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6174</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6127</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451981</t>
+          <t>452698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933686</t>
+          <t>933639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37733</t>
+          <t>36302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63592</t>
+          <t>64115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3383892</t>
+          <t>3385294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3405058</t>
+          <t>3405090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3511157</t>
+          <t>3512588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3532815</t>
+          <t>3533268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6905079</t>
+          <t>6904556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6932886</t>
+          <t>6933915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2016</t>
+          <t>Población con diagnóstico de angina de pecho en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>732097</t>
+          <t>732937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746277</t>
+          <t>746387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>970601</t>
+          <t>971521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>986987</t>
+          <t>987640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1710317</t>
+          <t>1709921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1731863</t>
+          <t>1730399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059923</t>
+          <t>2059919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072209</t>
+          <t>2072942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1977741</t>
+          <t>1976205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1987133</t>
+          <t>1987128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4041498</t>
+          <t>4042316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4057244</t>
+          <t>4057883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535129</t>
+          <t>534321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545957</t>
+          <t>545949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543962</t>
+          <t>544962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1082847</t>
+          <t>1084174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094864</t>
+          <t>1094881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3339303</t>
+          <t>3340348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3360218</t>
+          <t>3360204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3502653</t>
+          <t>3502711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521774</t>
+          <t>3521838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6849704</t>
+          <t>6849832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6876405</t>
+          <t>6876445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2023</t>
+          <t>Población con diagnóstico de angina de pecho en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29986</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494015</t>
+          <t>494182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505659</t>
+          <t>505978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>738364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>746998</t>
+          <t>747307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1235803</t>
+          <t>1236403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1251103</t>
+          <t>1250989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2267940</t>
+          <t>2267048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2281469</t>
+          <t>2280857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2221931</t>
+          <t>2222307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2230965</t>
+          <t>2231134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4494408</t>
+          <t>4493763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4510318</t>
+          <t>4510053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635225</t>
+          <t>635139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643773</t>
+          <t>643804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656273</t>
+          <t>655766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293369</t>
+          <t>1293603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302985</t>
+          <t>1302898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,47 +5017,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>48083</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>35961</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>60559</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>48083</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>37563</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>61749</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3404968</t>
+          <t>3405895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3426400</t>
+          <t>3426104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3623074</t>
+          <t>3622292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3635945</t>
+          <t>3635484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,47 +5130,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>8624</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>7047382</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>7034906</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7059504</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>99,32%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>8624</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>7047382</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>7033716</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7057902</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1412-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24205</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47463</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>952214</t>
+          <t>952607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>967300</t>
+          <t>967320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1303929</t>
+          <t>1304111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1322640</t>
+          <t>1322896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2263794</t>
+          <t>2261712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2287052</t>
+          <t>2285901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945364</t>
+          <t>1944610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959838</t>
+          <t>1959753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1746145</t>
+          <t>1746971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3695521</t>
+          <t>3696738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3712351</t>
+          <t>3711489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>452698</t>
+          <t>453252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933639</t>
+          <t>934557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>63573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3385294</t>
+          <t>3383398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3405090</t>
+          <t>3405216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3512588</t>
+          <t>3511879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3533268</t>
+          <t>3532498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6904556</t>
+          <t>6905098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6933915</t>
+          <t>6933714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39086</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>732937</t>
+          <t>732530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746387</t>
+          <t>746497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>971521</t>
+          <t>972357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>987640</t>
+          <t>987790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1709921</t>
+          <t>1710859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730399</t>
+          <t>1730960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2059919</t>
+          <t>2059784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2072942</t>
+          <t>2072115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1976205</t>
+          <t>1976347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1987128</t>
+          <t>1987039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4042316</t>
+          <t>4041403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4057883</t>
+          <t>4057360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534321</t>
+          <t>536095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545949</t>
+          <t>545970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544962</t>
+          <t>544665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084174</t>
+          <t>1082914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094881</t>
+          <t>1094997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33273</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59886</t>
+          <t>61909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3340348</t>
+          <t>3339288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3360204</t>
+          <t>3360137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3502711</t>
+          <t>3501721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521838</t>
+          <t>3520011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6849832</t>
+          <t>6847809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6876445</t>
+          <t>6877019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>501287</t>
+          <t>564017</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494182</t>
+          <t>555610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505978</t>
+          <t>569618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>743594</t>
+          <t>810252</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>738364</t>
+          <t>804661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>747307</t>
+          <t>814029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1244882</t>
+          <t>1374270</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1236403</t>
+          <t>1364606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250989</t>
+          <t>1381286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265789</t>
+          <t>1397459</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265789</t>
+          <t>1397459</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265789</t>
+          <t>1397459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29147</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2275558</t>
+          <t>2214318</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2267048</t>
+          <t>2205583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2280857</t>
+          <t>2219955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2227540</t>
+          <t>2159581</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2222307</t>
+          <t>2154318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2231134</t>
+          <t>2163632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4503098</t>
+          <t>4373898</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4493763</t>
+          <t>4363193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4510053</t>
+          <t>4380945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234660</t>
+          <t>2168223</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234660</t>
+          <t>2168223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234660</t>
+          <t>2168223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4522910</t>
+          <t>4396565</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4522910</t>
+          <t>4396565</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4522910</t>
+          <t>4396565</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640495</t>
+          <t>705068</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635139</t>
+          <t>699828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643804</t>
+          <t>708504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,27 +4767,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>658907</t>
+          <t>732219</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655766</t>
+          <t>729121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1299402</t>
+          <t>1437287</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293603</t>
+          <t>1431614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302898</t>
+          <t>1440910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41599</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>29724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>43044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>67513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3417341</t>
+          <t>3483402</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3405895</t>
+          <t>3471594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3426104</t>
+          <t>3492943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3630041</t>
+          <t>3702052</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3622292</t>
+          <t>3693300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3635484</t>
+          <t>3707912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7047382</t>
+          <t>7185454</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7034906</t>
+          <t>7171584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7059504</t>
+          <t>7196053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447494</t>
+          <t>3516073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447494</t>
+          <t>3516073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447494</t>
+          <t>3516073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647971</t>
+          <t>3723024</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647971</t>
+          <t>3723024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647971</t>
+          <t>3723024</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095465</t>
+          <t>7239097</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095465</t>
+          <t>7239097</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095465</t>
+          <t>7239097</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
